--- a/NECP Scenario/Results/Regional Results/RODOS_Generation.xlsx
+++ b/NECP Scenario/Results/Regional Results/RODOS_Generation.xlsx
@@ -563,25 +563,25 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>3.895036443271999E-08</v>
+        <v>5.7514132639863E-08</v>
       </c>
       <c r="C3">
-        <v>2.261419133202326E-08</v>
+        <v>3.33917010622692E-08</v>
       </c>
       <c r="D3">
-        <v>0.0434769920436922</v>
+        <v>0.05075386525197993</v>
       </c>
       <c r="E3">
-        <v>0.0404644412279985</v>
+        <v>0.04972527553949393</v>
       </c>
       <c r="F3">
-        <v>0.0862270363638904</v>
+        <v>0.2207763680538557</v>
       </c>
       <c r="G3">
-        <v>0.2261832046496239</v>
+        <v>0.3330052515920187</v>
       </c>
       <c r="H3">
-        <v>0.3033166789229648</v>
+        <v>0.6639112173879954</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -589,25 +589,25 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>3.310780977003384E-08</v>
+        <v>4.888701274568363E-08</v>
       </c>
       <c r="C4">
-        <v>1.922206263444163E-08</v>
+        <v>2.838294590472889E-08</v>
       </c>
       <c r="D4">
-        <v>0.03695544323713893</v>
+        <v>0.04314078546418426</v>
       </c>
       <c r="E4">
-        <v>0.03439477504377954</v>
+        <v>0.0422664842085576</v>
       </c>
       <c r="F4">
-        <v>0.07329298090931137</v>
+        <v>0.1876599128457049</v>
       </c>
       <c r="G4">
-        <v>0.1922557239519789</v>
+        <v>0.2830544638531961</v>
       </c>
       <c r="H4">
-        <v>0.2578191770845084</v>
+        <v>0.5643245347799751</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -849,25 +849,25 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>0.8166221189286629</v>
+        <v>0.8166221215978774</v>
       </c>
       <c r="C14">
-        <v>0.9286732389001969</v>
+        <v>0.9286732400822363</v>
       </c>
       <c r="D14">
-        <v>1.024493019023187</v>
+        <v>1.024492970381396</v>
       </c>
       <c r="E14">
-        <v>0.8138394649936401</v>
+        <v>0.8138394854614649</v>
       </c>
       <c r="F14">
-        <v>1.080357794313092</v>
+        <v>1.080357830917473</v>
       </c>
       <c r="G14">
-        <v>1.364333137620207</v>
+        <v>1.364333195054685</v>
       </c>
       <c r="H14">
-        <v>1.820784863386673</v>
+        <v>1.820785241929255</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1213,25 +1213,25 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>1.909368177225911</v>
+        <v>1.909368207713518</v>
       </c>
       <c r="C28">
-        <v>2.220367179200192</v>
+        <v>2.220367193640652</v>
       </c>
       <c r="D28">
-        <v>0.8071420599052235</v>
+        <v>0.8038355992030624</v>
       </c>
       <c r="E28">
-        <v>4.48788202801517E-08</v>
+        <v>6.563331317741108E-08</v>
       </c>
       <c r="F28">
-        <v>4.402041189695043E-08</v>
+        <v>6.472741711988184E-08</v>
       </c>
       <c r="G28">
-        <v>0.002168009151002685</v>
+        <v>0.002258726997416648</v>
       </c>
       <c r="H28">
-        <v>0.009519850500033658</v>
+        <v>0.006979774030302791</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -1239,25 +1239,25 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>0.7019735945555934</v>
+        <v>0.7019736057582007</v>
       </c>
       <c r="C29">
-        <v>0.8163114629348593</v>
+        <v>0.8163114682403213</v>
       </c>
       <c r="D29">
-        <v>0.2967434043674434</v>
+        <v>0.295527793810171</v>
       </c>
       <c r="E29">
-        <v>1.648513589466882E-08</v>
+        <v>2.410858412976703E-08</v>
       </c>
       <c r="F29">
-        <v>1.616275831142563E-08</v>
+        <v>2.376551547351903E-08</v>
       </c>
       <c r="G29">
-        <v>0.0007970621566758719</v>
+        <v>0.0008304142912281925</v>
       </c>
       <c r="H29">
-        <v>0.003499944847609677</v>
+        <v>0.002566093114228458</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1271,19 +1271,19 @@
         <v>0</v>
       </c>
       <c r="D30">
-        <v>0.7121341256943114</v>
+        <v>0.7143463130169702</v>
       </c>
       <c r="E30">
-        <v>1.312777180303596</v>
+        <v>1.302152875837552</v>
       </c>
       <c r="F30">
-        <v>1.314713674910315</v>
+        <v>1.311079410136266</v>
       </c>
       <c r="G30">
-        <v>1.317326322780379</v>
+        <v>1.314361632921137</v>
       </c>
       <c r="H30">
-        <v>1.318682389645929</v>
+        <v>1.319510781969414</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -1291,25 +1291,25 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>0.03574677388412348</v>
+        <v>0.03574677104806744</v>
       </c>
       <c r="C31">
-        <v>0.03574677722375253</v>
+        <v>0.03574677598297475</v>
       </c>
       <c r="D31">
-        <v>0.02281199105030006</v>
+        <v>0.02281248209352568</v>
       </c>
       <c r="E31">
-        <v>0.03443821725916923</v>
+        <v>0.03317094362543228</v>
       </c>
       <c r="F31">
-        <v>0.03474626950830962</v>
+        <v>0.03394300742411534</v>
       </c>
       <c r="G31">
-        <v>0.03527918312584268</v>
+        <v>0.03438795328056244</v>
       </c>
       <c r="H31">
-        <v>0.03555664902557351</v>
+        <v>0.03571732360527936</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1323,19 +1323,19 @@
         <v>0</v>
       </c>
       <c r="D32">
-        <v>1.495728661601594E-07</v>
+        <v>2.210843245261558E-07</v>
       </c>
       <c r="E32">
-        <v>0.4162460307735041</v>
+        <v>0.4162460618650656</v>
       </c>
       <c r="F32">
-        <v>0.4162660663233409</v>
+        <v>0.4162660479338843</v>
       </c>
       <c r="G32">
-        <v>0.4162660414498516</v>
+        <v>0.4162660125612203</v>
       </c>
       <c r="H32">
-        <v>0.4162657191992707</v>
+        <v>0.4162655270670035</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -1343,25 +1343,25 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>0.0434630395145782</v>
+        <v>0.0434630368612617</v>
       </c>
       <c r="C33">
-        <v>0.04346304262071957</v>
+        <v>0.04346304145125329</v>
       </c>
       <c r="D33">
-        <v>0.04346299723109984</v>
+        <v>0.04346297437477391</v>
       </c>
       <c r="E33">
-        <v>0.04344787639703183</v>
+        <v>0.04344782485570445</v>
       </c>
       <c r="F33">
-        <v>0.04346300810189268</v>
+        <v>0.04346298991367992</v>
       </c>
       <c r="G33">
-        <v>0.043462983420102</v>
+        <v>0.04346295491430727</v>
       </c>
       <c r="H33">
-        <v>0.0434626658966254</v>
+        <v>0.0434624797301549</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -1427,19 +1427,19 @@
         <v>0</v>
       </c>
       <c r="D36">
-        <v>1.550775162546454E-08</v>
+        <v>2.290478243244483E-08</v>
       </c>
       <c r="E36">
-        <v>1.333338970640242E-07</v>
+        <v>1.519944492482586E-07</v>
       </c>
       <c r="F36">
-        <v>4.521853236959425E-07</v>
+        <v>5.155749298000766E-07</v>
       </c>
       <c r="G36">
-        <v>9.289276067056308E-07</v>
+        <v>9.181654105614642E-07</v>
       </c>
       <c r="H36">
-        <v>4.191810854153449E-05</v>
+        <v>0.2791160858253081</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -1447,25 +1447,25 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>0.09556751389430555</v>
+        <v>0.09556751105362825</v>
       </c>
       <c r="C37">
-        <v>0.09556751724055754</v>
+        <v>0.09556751599845119</v>
       </c>
       <c r="D37">
-        <v>0.02023305203463894</v>
+        <v>0.02032745818642138</v>
       </c>
       <c r="E37">
-        <v>0.07725354099324885</v>
+        <v>0.06870168883791987</v>
       </c>
       <c r="F37">
-        <v>0.08030029890457162</v>
+        <v>0.07385859392047478</v>
       </c>
       <c r="G37">
-        <v>0.08440233500373566</v>
+        <v>0.0791562214708806</v>
       </c>
       <c r="H37">
-        <v>0.09166340863978553</v>
+        <v>0.08951654670814764</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -1473,25 +1473,25 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>1.743912120698669E-08</v>
+        <v>2.576917105788056E-08</v>
       </c>
       <c r="C38">
-        <v>7.647098818295138E-09</v>
+        <v>1.129944914503071E-08</v>
       </c>
       <c r="D38">
-        <v>0.3965362723453644</v>
+        <v>0.3949281140787496</v>
       </c>
       <c r="E38">
-        <v>0.02643965826287331</v>
+        <v>0.04688312228142939</v>
       </c>
       <c r="F38">
-        <v>0.02111324873853905</v>
+        <v>0.03199255026746535</v>
       </c>
       <c r="G38">
-        <v>0.01386578755252177</v>
+        <v>0.02296791271953461</v>
       </c>
       <c r="H38">
-        <v>0.004975754978643783</v>
+        <v>0.02428721942452569</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -1525,25 +1525,25 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>3.895036443271999E-08</v>
+        <v>5.7514132639863E-08</v>
       </c>
       <c r="C40">
-        <v>2.261419133202326E-08</v>
+        <v>3.33917010622692E-08</v>
       </c>
       <c r="D40">
-        <v>0.0434769920436922</v>
+        <v>0.05075386525197993</v>
       </c>
       <c r="E40">
-        <v>0.0404644412279985</v>
+        <v>0.04972527553949393</v>
       </c>
       <c r="F40">
-        <v>0.0862270363638904</v>
+        <v>0.2207763680538557</v>
       </c>
       <c r="G40">
-        <v>0.2261832046496239</v>
+        <v>0.3330052515920187</v>
       </c>
       <c r="H40">
-        <v>0.3033166789229648</v>
+        <v>0.6639112173879954</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -1551,25 +1551,25 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>3.310780977003384E-08</v>
+        <v>4.888701274568363E-08</v>
       </c>
       <c r="C41">
-        <v>1.922206263444163E-08</v>
+        <v>2.838294590472889E-08</v>
       </c>
       <c r="D41">
-        <v>0.03695544323713893</v>
+        <v>0.04314078546418426</v>
       </c>
       <c r="E41">
-        <v>0.03439477504377954</v>
+        <v>0.0422664842085576</v>
       </c>
       <c r="F41">
-        <v>0.07329298090931137</v>
+        <v>0.1876599128457049</v>
       </c>
       <c r="G41">
-        <v>0.1922557239519789</v>
+        <v>0.2830544638531961</v>
       </c>
       <c r="H41">
-        <v>0.2578191770845084</v>
+        <v>0.5643245347799751</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -1577,25 +1577,25 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>-5.842554662686151E-09</v>
+        <v>-8.627119894179373E-09</v>
       </c>
       <c r="C42">
-        <v>-3.392128697581633E-09</v>
+        <v>-5.008755157540306E-09</v>
       </c>
       <c r="D42">
-        <v>-0.006521548806553271</v>
+        <v>-0.007613079787795664</v>
       </c>
       <c r="E42">
-        <v>-0.006069666184218961</v>
+        <v>-0.007458791330936333</v>
       </c>
       <c r="F42">
-        <v>-0.01293405545457903</v>
+        <v>-0.03311645520815082</v>
       </c>
       <c r="G42">
-        <v>-0.03392748069764498</v>
+        <v>-0.04995078773882256</v>
       </c>
       <c r="H42">
-        <v>-0.04549750183845641</v>
+        <v>-0.09958668260802028</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -1612,16 +1612,16 @@
         <v>-0</v>
       </c>
       <c r="E43">
-        <v>-0.587950988482161</v>
+        <v>-0.5661184384622588</v>
       </c>
       <c r="F43">
-        <v>-0.3144207435957209</v>
+        <v>-0.2833591456125559</v>
       </c>
       <c r="G43">
-        <v>-0.01170168017138654</v>
+        <v>0.01339037738236611</v>
       </c>
       <c r="H43">
-        <v>0.4539969302326531</v>
+        <v>0.2311039765593867</v>
       </c>
     </row>
     <row r="44" spans="1:8">
